--- a/data_lake/macro/Japan/Japan Interest Rate.xlsx
+++ b/data_lake/macro/Japan/Japan Interest Rate.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data_lake\macro\Japan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2164DE32-20CD-4011-BAEF-BF0ACA1C64DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4696177-BB62-451C-B6EF-F11DC220BD28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{BD32588E-2B16-4C89-A5B1-1458B27ABC9F}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{BD32588E-2B16-4C89-A5B1-1458B27ABC9F}"/>
   </bookViews>
   <sheets>
     <sheet name="BOJDTR" sheetId="1" r:id="rId1"/>

--- a/data_lake/macro/Japan/Japan Interest Rate.xlsx
+++ b/data_lake/macro/Japan/Japan Interest Rate.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data_lake\macro\Japan\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/junghunlee/Desktop/Pycharm/FinancialData/data_lake/macro/Japan/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4696177-BB62-451C-B6EF-F11DC220BD28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B02C94F9-06EE-F84D-A49C-937E66560775}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{BD32588E-2B16-4C89-A5B1-1458B27ABC9F}"/>
+    <workbookView xWindow="13820" yWindow="780" windowWidth="22180" windowHeight="20800" xr2:uid="{BD32588E-2B16-4C89-A5B1-1458B27ABC9F}"/>
   </bookViews>
   <sheets>
     <sheet name="BOJDTR" sheetId="1" r:id="rId1"/>
@@ -75,21 +75,21 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="177" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="165" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
   </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -98,7 +98,7 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -107,7 +107,7 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -115,7 +115,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -162,7 +162,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -175,31 +175,25 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="20" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="5" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -210,9 +204,9 @@
     </xf>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="백분율" xfId="2" builtinId="5"/>
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
-    <cellStyle name="하이퍼링크" xfId="1" builtinId="8"/>
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -228,9 +222,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -268,7 +262,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -374,7 +368,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -516,7 +510,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -525,21 +519,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFA4B462-8401-43D4-A97D-0B68FA77EED7}">
   <dimension ref="A1:H201"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.796875" style="12" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.19921875" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.3984375" style="9" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.1640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.33203125" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.83203125" style="9" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9" style="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.796875" style="14" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.796875" style="14" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.69921875" style="14" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="23.3984375" style="6" customWidth="1"/>
+    <col min="5" max="5" width="7.83203125" style="12" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.83203125" style="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.6640625" style="12" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="23.33203125" style="6" customWidth="1"/>
     <col min="9" max="16384" width="9" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1" s="4" t="s">
         <v>11</v>
       </c>
       <c r="B1" s="4" t="s">
@@ -551,17 +545,17 @@
       <c r="D1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="G1" s="11" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="8">
         <v>39492</v>
       </c>
@@ -574,17 +568,17 @@
       <c r="D2" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="14">
+      <c r="E2" s="12">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="F2" s="14">
+      <c r="F2" s="12">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="G2" s="14">
+      <c r="G2" s="12">
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="8">
         <v>39514</v>
       </c>
@@ -597,17 +591,17 @@
       <c r="D3" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="14">
+      <c r="E3" s="12">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="F3" s="14">
+      <c r="F3" s="12">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="G3" s="14">
+      <c r="G3" s="12">
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="8">
         <v>39547</v>
       </c>
@@ -620,17 +614,17 @@
       <c r="D4" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E4" s="14">
+      <c r="E4" s="12">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="F4" s="14">
+      <c r="F4" s="12">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="G4" s="14">
+      <c r="G4" s="12">
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="8">
         <v>39568</v>
       </c>
@@ -643,17 +637,17 @@
       <c r="D5" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E5" s="14">
+      <c r="E5" s="12">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="F5" s="14">
+      <c r="F5" s="12">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="G5" s="14">
+      <c r="G5" s="12">
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="8">
         <v>39612</v>
       </c>
@@ -666,17 +660,17 @@
       <c r="D6" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E6" s="14">
+      <c r="E6" s="12">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="F6" s="14">
+      <c r="F6" s="12">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="G6" s="14">
+      <c r="G6" s="12">
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="8">
         <v>39644</v>
       </c>
@@ -689,17 +683,17 @@
       <c r="D7" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E7" s="14">
+      <c r="E7" s="12">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="F7" s="14">
+      <c r="F7" s="12">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="G7" s="14">
+      <c r="G7" s="12">
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="8">
         <v>39679</v>
       </c>
@@ -712,17 +706,17 @@
       <c r="D8" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E8" s="14">
+      <c r="E8" s="12">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="F8" s="14">
+      <c r="F8" s="12">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="G8" s="14">
+      <c r="G8" s="12">
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" s="8">
         <v>39708</v>
       </c>
@@ -735,17 +729,17 @@
       <c r="D9" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E9" s="14">
+      <c r="E9" s="12">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="F9" s="14">
+      <c r="F9" s="12">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="G9" s="14">
+      <c r="G9" s="12">
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" s="8">
         <v>39728</v>
       </c>
@@ -758,17 +752,17 @@
       <c r="D10" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E10" s="14">
+      <c r="E10" s="12">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="F10" s="14">
+      <c r="F10" s="12">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="G10" s="14">
+      <c r="G10" s="12">
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" s="8">
         <v>39752</v>
       </c>
@@ -781,17 +775,17 @@
       <c r="D11" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E11" s="14">
+      <c r="E11" s="12">
         <v>3.0000000000000001E-3</v>
       </c>
-      <c r="F11" s="14">
+      <c r="F11" s="12">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="G11" s="14">
+      <c r="G11" s="12">
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" s="8">
         <v>39773</v>
       </c>
@@ -804,17 +798,17 @@
       <c r="D12" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E12" s="14">
+      <c r="E12" s="12">
         <v>3.0000000000000001E-3</v>
       </c>
-      <c r="F12" s="14">
+      <c r="F12" s="12">
         <v>3.0000000000000001E-3</v>
       </c>
-      <c r="G12" s="14">
+      <c r="G12" s="12">
         <v>3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="8">
         <v>39784</v>
       </c>
@@ -827,17 +821,17 @@
       <c r="D13" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E13" s="14">
+      <c r="E13" s="12">
         <v>3.0000000000000001E-3</v>
       </c>
-      <c r="F13" s="14">
+      <c r="F13" s="12">
         <v>3.0000000000000001E-3</v>
       </c>
-      <c r="G13" s="14">
+      <c r="G13" s="12">
         <v>3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" s="8">
         <v>39801</v>
       </c>
@@ -850,17 +844,17 @@
       <c r="D14" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E14" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="F14" s="14">
+      <c r="E14" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="F14" s="12">
         <v>3.0000000000000001E-3</v>
       </c>
-      <c r="G14" s="14">
+      <c r="G14" s="12">
         <v>3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" s="8">
         <v>39835</v>
       </c>
@@ -873,17 +867,17 @@
       <c r="D15" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E15" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="F15" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="G15" s="14">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E15" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="F15" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="G15" s="12">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" s="8">
         <v>39889</v>
       </c>
@@ -896,17 +890,17 @@
       <c r="D16" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E16" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="F16" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="G16" s="14">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E16" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="F16" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="G16" s="12">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" s="8">
         <v>39910</v>
       </c>
@@ -919,17 +913,17 @@
       <c r="D17" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E17" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="F17" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="G17" s="14">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E17" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="F17" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="G17" s="12">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" s="8">
         <v>39933</v>
       </c>
@@ -942,17 +936,17 @@
       <c r="D18" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E18" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="F18" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="G18" s="14">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E18" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="F18" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="G18" s="12">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" s="8">
         <v>39955</v>
       </c>
@@ -965,17 +959,17 @@
       <c r="D19" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E19" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="F19" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="G19" s="14">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E19" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="F19" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="G19" s="12">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" s="8">
         <v>39980</v>
       </c>
@@ -988,17 +982,17 @@
       <c r="D20" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E20" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="F20" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="G20" s="14">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E20" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="F20" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="G20" s="12">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" s="8">
         <v>40009</v>
       </c>
@@ -1011,17 +1005,17 @@
       <c r="D21" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E21" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="F21" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="G21" s="14">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E21" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="F21" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="G21" s="12">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" s="8">
         <v>40036</v>
       </c>
@@ -1034,17 +1028,17 @@
       <c r="D22" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E22" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="F22" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="G22" s="14">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E22" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="F22" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="G22" s="12">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" s="8">
         <v>40073</v>
       </c>
@@ -1057,17 +1051,17 @@
       <c r="D23" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E23" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="F23" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="G23" s="14">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E23" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="F23" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="G23" s="12">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" s="8">
         <v>40100</v>
       </c>
@@ -1080,17 +1074,17 @@
       <c r="D24" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E24" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="F24" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="G24" s="14">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E24" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="F24" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="G24" s="12">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" s="8">
         <v>40116</v>
       </c>
@@ -1103,17 +1097,17 @@
       <c r="D25" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E25" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="F25" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="G25" s="14">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E25" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="F25" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="G25" s="12">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" s="8">
         <v>40137</v>
       </c>
@@ -1126,17 +1120,17 @@
       <c r="D26" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E26" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="F26" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="G26" s="14">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E26" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="F26" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="G26" s="12">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" s="8">
         <v>40148</v>
       </c>
@@ -1149,14 +1143,14 @@
       <c r="D27" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E27" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="G27" s="14">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E27" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="G27" s="12">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" s="8">
         <v>40165</v>
       </c>
@@ -1169,17 +1163,17 @@
       <c r="D28" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E28" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="F28" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="G28" s="14">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E28" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="F28" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="G28" s="12">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" s="8">
         <v>40204</v>
       </c>
@@ -1192,17 +1186,17 @@
       <c r="D29" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E29" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="F29" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="G29" s="14">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E29" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="F29" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="G29" s="12">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" s="8">
         <v>40227</v>
       </c>
@@ -1215,17 +1209,17 @@
       <c r="D30" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E30" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="F30" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="G30" s="14">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E30" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="F30" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="G30" s="12">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" s="8">
         <v>40254</v>
       </c>
@@ -1238,17 +1232,17 @@
       <c r="D31" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E31" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="F31" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="G31" s="14">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E31" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="F31" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="G31" s="12">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" s="8">
         <v>40275</v>
       </c>
@@ -1261,17 +1255,17 @@
       <c r="D32" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E32" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="F32" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="G32" s="14">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E32" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="F32" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="G32" s="12">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" s="8">
         <v>40298</v>
       </c>
@@ -1284,17 +1278,17 @@
       <c r="D33" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E33" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="F33" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="G33" s="14">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E33" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="F33" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="G33" s="12">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" s="8">
         <v>40308</v>
       </c>
@@ -1307,17 +1301,17 @@
       <c r="D34" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E34" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="F34" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="G34" s="14">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E34" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="F34" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="G34" s="12">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" s="8">
         <v>40319</v>
       </c>
@@ -1330,17 +1324,17 @@
       <c r="D35" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E35" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="F35" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="G35" s="14">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E35" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="F35" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="G35" s="12">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" s="8">
         <v>40344</v>
       </c>
@@ -1353,17 +1347,17 @@
       <c r="D36" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E36" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="F36" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="G36" s="14">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E36" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="F36" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="G36" s="12">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" s="8">
         <v>40374</v>
       </c>
@@ -1376,17 +1370,17 @@
       <c r="D37" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E37" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="F37" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="G37" s="14">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E37" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="F37" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="G37" s="12">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" s="8">
         <v>40400</v>
       </c>
@@ -1399,17 +1393,17 @@
       <c r="D38" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E38" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="F38" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="G38" s="14">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E38" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="F38" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="G38" s="12">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" s="8">
         <v>40420</v>
       </c>
@@ -1422,17 +1416,17 @@
       <c r="D39" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E39" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="F39" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="G39" s="14">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E39" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="F39" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="G39" s="12">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" s="8">
         <v>40428</v>
       </c>
@@ -1445,17 +1439,17 @@
       <c r="D40" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E40" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="F40" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="G40" s="14">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E40" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="F40" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="G40" s="12">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" s="8">
         <v>40456</v>
       </c>
@@ -1468,17 +1462,17 @@
       <c r="D41" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E41" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="F41" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="G41" s="14">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E41" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="F41" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="G41" s="12">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" s="8">
         <v>40479</v>
       </c>
@@ -1491,17 +1485,17 @@
       <c r="D42" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E42" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="F42" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="G42" s="14">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E42" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="F42" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="G42" s="12">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" s="8">
         <v>40487</v>
       </c>
@@ -1514,17 +1508,17 @@
       <c r="D43" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E43" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="F43" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="G43" s="14">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E43" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="F43" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="G43" s="12">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" s="8">
         <v>40533</v>
       </c>
@@ -1537,17 +1531,17 @@
       <c r="D44" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E44" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="F44" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="G44" s="14">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E44" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="F44" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="G44" s="12">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45" s="8">
         <v>40568</v>
       </c>
@@ -1560,17 +1554,17 @@
       <c r="D45" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E45" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="F45" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="G45" s="14">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E45" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="F45" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="G45" s="12">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A46" s="8">
         <v>40589</v>
       </c>
@@ -1583,17 +1577,17 @@
       <c r="D46" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E46" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="F46" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="G46" s="14">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E46" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="F46" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="G46" s="12">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A47" s="8">
         <v>40616</v>
       </c>
@@ -1606,17 +1600,17 @@
       <c r="D47" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E47" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="F47" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="G47" s="14">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E47" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="F47" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="G47" s="12">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A48" s="8">
         <v>40640</v>
       </c>
@@ -1629,17 +1623,17 @@
       <c r="D48" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E48" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="F48" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="G48" s="14">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E48" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="F48" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="G48" s="12">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A49" s="8">
         <v>40661</v>
       </c>
@@ -1652,17 +1646,17 @@
       <c r="D49" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E49" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="F49" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="G49" s="14">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E49" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="F49" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="G49" s="12">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A50" s="8">
         <v>40683</v>
       </c>
@@ -1675,17 +1669,17 @@
       <c r="D50" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E50" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="F50" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="G50" s="14">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E50" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="F50" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="G50" s="12">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A51" s="8">
         <v>40708</v>
       </c>
@@ -1698,17 +1692,17 @@
       <c r="D51" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E51" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="F51" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="G51" s="14">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E51" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="F51" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="G51" s="12">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A52" s="8">
         <v>40736</v>
       </c>
@@ -1721,17 +1715,17 @@
       <c r="D52" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E52" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="F52" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="G52" s="14">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E52" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="F52" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="G52" s="12">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A53" s="8">
         <v>40759</v>
       </c>
@@ -1744,17 +1738,17 @@
       <c r="D53" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E53" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="F53" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="G53" s="14">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E53" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="F53" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="G53" s="12">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A54" s="8">
         <v>40793</v>
       </c>
@@ -1767,17 +1761,17 @@
       <c r="D54" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E54" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="F54" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="G54" s="14">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E54" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="F54" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="G54" s="12">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A55" s="8">
         <v>40823</v>
       </c>
@@ -1790,17 +1784,17 @@
       <c r="D55" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E55" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="F55" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="G55" s="14">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E55" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="F55" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="G55" s="12">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A56" s="8">
         <v>40843</v>
       </c>
@@ -1813,17 +1807,17 @@
       <c r="D56" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E56" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="F56" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="G56" s="14">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E56" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="F56" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="G56" s="12">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A57" s="8">
         <v>40863</v>
       </c>
@@ -1836,17 +1830,17 @@
       <c r="D57" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E57" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="F57" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="G57" s="14">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E57" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="F57" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="G57" s="12">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A58" s="8">
         <v>40898</v>
       </c>
@@ -1859,17 +1853,17 @@
       <c r="D58" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E58" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="F58" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="G58" s="14">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E58" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="F58" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="G58" s="12">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A59" s="8">
         <v>40932</v>
       </c>
@@ -1882,17 +1876,17 @@
       <c r="D59" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E59" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="F59" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="G59" s="14">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E59" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="F59" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="G59" s="12">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A60" s="8">
         <v>40953</v>
       </c>
@@ -1905,17 +1899,17 @@
       <c r="D60" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E60" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="F60" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="G60" s="14">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E60" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="F60" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="G60" s="12">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A61" s="8">
         <v>40981</v>
       </c>
@@ -1928,17 +1922,17 @@
       <c r="D61" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E61" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="F61" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="G61" s="14">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E61" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="F61" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="G61" s="12">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A62" s="8">
         <v>41009</v>
       </c>
@@ -1951,17 +1945,17 @@
       <c r="D62" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E62" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="F62" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="G62" s="14">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E62" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="F62" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="G62" s="12">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A63" s="8">
         <v>41026</v>
       </c>
@@ -1974,17 +1968,17 @@
       <c r="D63" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E63" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="F63" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="G63" s="14">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E63" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="F63" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="G63" s="12">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A64" s="8">
         <v>41052</v>
       </c>
@@ -1997,17 +1991,17 @@
       <c r="D64" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E64" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="F64" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="G64" s="14">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E64" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="F64" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="G64" s="12">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A65" s="8">
         <v>41075</v>
       </c>
@@ -2020,17 +2014,17 @@
       <c r="D65" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E65" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="F65" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="G65" s="14">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E65" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="F65" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="G65" s="12">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A66" s="8">
         <v>41102</v>
       </c>
@@ -2043,17 +2037,17 @@
       <c r="D66" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E66" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="F66" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="G66" s="14">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E66" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="F66" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="G66" s="12">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A67" s="8">
         <v>41130</v>
       </c>
@@ -2066,17 +2060,17 @@
       <c r="D67" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E67" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="F67" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="G67" s="14">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E67" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="F67" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="G67" s="12">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A68" s="8">
         <v>41171</v>
       </c>
@@ -2089,17 +2083,17 @@
       <c r="D68" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E68" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="F68" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="G68" s="14">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E68" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="F68" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="G68" s="12">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A69" s="8">
         <v>41187</v>
       </c>
@@ -2112,17 +2106,17 @@
       <c r="D69" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E69" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="F69" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="G69" s="14">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E69" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="F69" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="G69" s="12">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A70" s="8">
         <v>41212</v>
       </c>
@@ -2135,17 +2129,17 @@
       <c r="D70" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E70" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="F70" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="G70" s="14">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E70" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="F70" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="G70" s="12">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A71" s="8">
         <v>41233</v>
       </c>
@@ -2158,17 +2152,17 @@
       <c r="D71" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E71" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="F71" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="G71" s="14">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E71" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="F71" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="G71" s="12">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A72" s="8">
         <v>41263</v>
       </c>
@@ -2181,17 +2175,17 @@
       <c r="D72" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E72" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="F72" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="G72" s="14">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E72" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="F72" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="G72" s="12">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A73" s="8">
         <v>41296</v>
       </c>
@@ -2204,17 +2198,17 @@
       <c r="D73" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E73" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="F73" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="G73" s="14">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E73" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="F73" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="G73" s="12">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A74" s="8">
         <v>41319</v>
       </c>
@@ -2227,17 +2221,17 @@
       <c r="D74" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E74" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="F74" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="G74" s="14">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E74" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="F74" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="G74" s="12">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A75" s="8">
         <v>41340</v>
       </c>
@@ -2250,17 +2244,17 @@
       <c r="D75" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E75" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="F75" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="G75" s="14">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E75" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="F75" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="G75" s="12">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A76" s="8">
         <v>41368</v>
       </c>
@@ -2273,17 +2267,17 @@
       <c r="D76" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E76" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="F76" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="G76" s="14">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E76" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="F76" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="G76" s="12">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A77" s="8">
         <v>41390</v>
       </c>
@@ -2296,17 +2290,17 @@
       <c r="D77" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E77" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="F77" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="G77" s="14">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E77" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="F77" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="G77" s="12">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A78" s="8">
         <v>41416</v>
       </c>
@@ -2319,17 +2313,17 @@
       <c r="D78" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E78" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="F78" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="G78" s="14">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E78" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="F78" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="G78" s="12">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A79" s="8">
         <v>41436</v>
       </c>
@@ -2342,17 +2336,17 @@
       <c r="D79" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E79" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="F79" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="G79" s="14">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E79" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="F79" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="G79" s="12">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A80" s="8">
         <v>41466</v>
       </c>
@@ -2365,17 +2359,17 @@
       <c r="D80" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E80" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="F80" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="G80" s="14">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E80" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="F80" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="G80" s="12">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A81" s="8">
         <v>41494</v>
       </c>
@@ -2388,17 +2382,17 @@
       <c r="D81" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E81" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="F81" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="G81" s="14">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E81" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="F81" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="G81" s="12">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A82" s="8">
         <v>41522</v>
       </c>
@@ -2411,17 +2405,17 @@
       <c r="D82" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E82" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="F82" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="G82" s="14">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E82" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="F82" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="G82" s="12">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A83" s="8">
         <v>41551</v>
       </c>
@@ -2434,17 +2428,17 @@
       <c r="D83" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E83" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="F83" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="G83" s="14">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E83" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="F83" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="G83" s="12">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A84" s="8">
         <v>41578</v>
       </c>
@@ -2457,17 +2451,17 @@
       <c r="D84" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E84" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="F84" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="G84" s="14">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E84" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="F84" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="G84" s="12">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A85" s="8">
         <v>41599</v>
       </c>
@@ -2480,17 +2474,17 @@
       <c r="D85" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E85" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="F85" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="G85" s="14">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E85" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="F85" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="G85" s="12">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A86" s="8">
         <v>41628</v>
       </c>
@@ -2503,17 +2497,17 @@
       <c r="D86" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E86" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="F86" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="G86" s="14">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E86" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="F86" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="G86" s="12">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A87" s="8">
         <v>41661</v>
       </c>
@@ -2526,17 +2520,17 @@
       <c r="D87" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E87" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="F87" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="G87" s="14">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E87" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="F87" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="G87" s="12">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A88" s="8">
         <v>41688</v>
       </c>
@@ -2549,17 +2543,17 @@
       <c r="D88" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E88" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="F88" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="G88" s="14">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E88" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="F88" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="G88" s="12">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A89" s="8">
         <v>41709</v>
       </c>
@@ -2572,17 +2566,17 @@
       <c r="D89" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E89" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="F89" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="G89" s="14">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E89" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="F89" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="G89" s="12">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A90" s="8">
         <v>41737</v>
       </c>
@@ -2595,17 +2589,17 @@
       <c r="D90" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E90" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="F90" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="G90" s="14">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E90" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="F90" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="G90" s="12">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A91" s="8">
         <v>41759</v>
       </c>
@@ -2618,17 +2612,17 @@
       <c r="D91" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E91" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="F91" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="G91" s="14">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E91" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="F91" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="G91" s="12">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A92" s="8">
         <v>41780</v>
       </c>
@@ -2641,17 +2635,17 @@
       <c r="D92" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E92" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="F92" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="G92" s="14">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E92" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="F92" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="G92" s="12">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A93" s="8">
         <v>41803</v>
       </c>
@@ -2664,17 +2658,17 @@
       <c r="D93" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E93" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="F93" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="G93" s="14">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E93" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="F93" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="G93" s="12">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A94" s="8">
         <v>41835</v>
       </c>
@@ -2687,17 +2681,17 @@
       <c r="D94" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E94" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="F94" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="G94" s="14">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E94" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="F94" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="G94" s="12">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A95" s="8">
         <v>41859</v>
       </c>
@@ -2710,17 +2704,17 @@
       <c r="D95" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E95" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="F95" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="G95" s="14">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E95" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="F95" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="G95" s="12">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A96" s="8">
         <v>41886</v>
       </c>
@@ -2733,17 +2727,17 @@
       <c r="D96" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E96" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="F96" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="G96" s="14">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E96" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="F96" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="G96" s="12">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A97" s="8">
         <v>41919</v>
       </c>
@@ -2756,17 +2750,17 @@
       <c r="D97" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E97" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="F97" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="G97" s="14">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E97" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="F97" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="G97" s="12">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A98" s="8">
         <v>41943</v>
       </c>
@@ -2779,17 +2773,17 @@
       <c r="D98" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E98" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="F98" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="G98" s="14">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E98" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="F98" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="G98" s="12">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A99" s="8">
         <v>41962</v>
       </c>
@@ -2802,17 +2796,17 @@
       <c r="D99" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E99" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="F99" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="G99" s="14">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E99" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="F99" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="G99" s="12">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A100" s="8">
         <v>41992</v>
       </c>
@@ -2825,17 +2819,17 @@
       <c r="D100" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E100" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="F100" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="G100" s="14">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E100" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="F100" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="G100" s="12">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A101" s="8">
         <v>42025</v>
       </c>
@@ -2848,17 +2842,17 @@
       <c r="D101" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E101" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="F101" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="G101" s="14">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E101" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="F101" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="G101" s="12">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A102" s="8">
         <v>42053</v>
       </c>
@@ -2871,17 +2865,17 @@
       <c r="D102" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E102" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="F102" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="G102" s="14">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E102" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="F102" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="G102" s="12">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A103" s="8">
         <v>42080</v>
       </c>
@@ -2894,17 +2888,17 @@
       <c r="D103" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E103" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="F103" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="G103" s="14">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E103" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="F103" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="G103" s="12">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A104" s="8">
         <v>42102</v>
       </c>
@@ -2917,17 +2911,17 @@
       <c r="D104" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E104" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="F104" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="G104" s="14">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E104" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="F104" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="G104" s="12">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A105" s="8">
         <v>42124</v>
       </c>
@@ -2940,17 +2934,17 @@
       <c r="D105" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E105" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="F105" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="G105" s="14">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E105" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="F105" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="G105" s="12">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A106" s="8">
         <v>42146</v>
       </c>
@@ -2963,17 +2957,17 @@
       <c r="D106" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E106" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="F106" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="G106" s="14">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E106" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="F106" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="G106" s="12">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A107" s="8">
         <v>42174</v>
       </c>
@@ -2986,17 +2980,17 @@
       <c r="D107" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E107" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="F107" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="G107" s="14">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E107" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="F107" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="G107" s="12">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A108" s="8">
         <v>42200</v>
       </c>
@@ -3009,17 +3003,17 @@
       <c r="D108" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E108" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="F108" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="G108" s="14">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E108" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="F108" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="G108" s="12">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A109" s="8">
         <v>42223</v>
       </c>
@@ -3032,17 +3026,17 @@
       <c r="D109" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E109" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="F109" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="G109" s="14">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E109" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="F109" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="G109" s="12">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A110" s="8">
         <v>42262</v>
       </c>
@@ -3055,17 +3049,17 @@
       <c r="D110" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E110" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="F110" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="G110" s="14">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E110" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="F110" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="G110" s="12">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A111" s="8">
         <v>42284</v>
       </c>
@@ -3078,17 +3072,17 @@
       <c r="D111" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E111" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="F111" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="G111" s="14">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E111" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="F111" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="G111" s="12">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A112" s="8">
         <v>42307</v>
       </c>
@@ -3101,17 +3095,17 @@
       <c r="D112" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E112" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="F112" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="G112" s="14">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E112" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="F112" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="G112" s="12">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A113" s="8">
         <v>42327</v>
       </c>
@@ -3124,17 +3118,17 @@
       <c r="D113" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E113" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="F113" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="G113" s="14">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E113" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="F113" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="G113" s="12">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A114" s="8">
         <v>42356</v>
       </c>
@@ -3147,17 +3141,17 @@
       <c r="D114" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E114" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="F114" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="G114" s="14">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E114" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="F114" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="G114" s="12">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A115" s="8">
         <v>42398</v>
       </c>
@@ -3170,17 +3164,17 @@
       <c r="D115" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E115" s="14">
-        <v>-1E-3</v>
-      </c>
-      <c r="F115" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="G115" s="14">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E115" s="12">
+        <v>-1E-3</v>
+      </c>
+      <c r="F115" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="G115" s="12">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A116" s="8">
         <v>42444</v>
       </c>
@@ -3193,17 +3187,17 @@
       <c r="D116" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E116" s="14">
-        <v>-1E-3</v>
-      </c>
-      <c r="F116" s="14">
-        <v>-1E-3</v>
-      </c>
-      <c r="G116" s="14">
-        <v>-1E-3</v>
-      </c>
-    </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E116" s="12">
+        <v>-1E-3</v>
+      </c>
+      <c r="F116" s="12">
+        <v>-1E-3</v>
+      </c>
+      <c r="G116" s="12">
+        <v>-1E-3</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A117" s="8">
         <v>42488</v>
       </c>
@@ -3216,17 +3210,17 @@
       <c r="D117" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E117" s="14">
-        <v>-1E-3</v>
-      </c>
-      <c r="F117" s="14">
-        <v>-1E-3</v>
-      </c>
-      <c r="G117" s="14">
-        <v>-1E-3</v>
-      </c>
-    </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E117" s="12">
+        <v>-1E-3</v>
+      </c>
+      <c r="F117" s="12">
+        <v>-1E-3</v>
+      </c>
+      <c r="G117" s="12">
+        <v>-1E-3</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A118" s="8">
         <v>42537</v>
       </c>
@@ -3239,17 +3233,17 @@
       <c r="D118" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E118" s="14">
-        <v>-1E-3</v>
-      </c>
-      <c r="F118" s="14">
-        <v>-1E-3</v>
-      </c>
-      <c r="G118" s="14">
-        <v>-1E-3</v>
-      </c>
-    </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E118" s="12">
+        <v>-1E-3</v>
+      </c>
+      <c r="F118" s="12">
+        <v>-1E-3</v>
+      </c>
+      <c r="G118" s="12">
+        <v>-1E-3</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A119" s="8">
         <v>42580</v>
       </c>
@@ -3262,17 +3256,17 @@
       <c r="D119" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E119" s="14">
-        <v>-1E-3</v>
-      </c>
-      <c r="F119" s="14">
+      <c r="E119" s="12">
+        <v>-1E-3</v>
+      </c>
+      <c r="F119" s="12">
         <v>-1.5E-3</v>
       </c>
-      <c r="G119" s="14">
-        <v>-1E-3</v>
-      </c>
-    </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="G119" s="12">
+        <v>-1E-3</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A120" s="8">
         <v>42634</v>
       </c>
@@ -3285,17 +3279,17 @@
       <c r="D120" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E120" s="14">
-        <v>-1E-3</v>
-      </c>
-      <c r="F120" s="14">
+      <c r="E120" s="12">
+        <v>-1E-3</v>
+      </c>
+      <c r="F120" s="12">
         <v>-1.5E-3</v>
       </c>
-      <c r="G120" s="14">
-        <v>-1E-3</v>
-      </c>
-    </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="G120" s="12">
+        <v>-1E-3</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A121" s="8">
         <v>42675</v>
       </c>
@@ -3308,17 +3302,17 @@
       <c r="D121" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E121" s="14">
-        <v>-1E-3</v>
-      </c>
-      <c r="F121" s="14">
-        <v>-1E-3</v>
-      </c>
-      <c r="G121" s="14">
-        <v>-1E-3</v>
-      </c>
-    </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E121" s="12">
+        <v>-1E-3</v>
+      </c>
+      <c r="F121" s="12">
+        <v>-1E-3</v>
+      </c>
+      <c r="G121" s="12">
+        <v>-1E-3</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A122" s="8">
         <v>42724</v>
       </c>
@@ -3331,17 +3325,17 @@
       <c r="D122" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E122" s="14">
-        <v>-1E-3</v>
-      </c>
-      <c r="F122" s="14">
-        <v>-1E-3</v>
-      </c>
-      <c r="G122" s="14">
-        <v>-1E-3</v>
-      </c>
-    </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E122" s="12">
+        <v>-1E-3</v>
+      </c>
+      <c r="F122" s="12">
+        <v>-1E-3</v>
+      </c>
+      <c r="G122" s="12">
+        <v>-1E-3</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A123" s="8">
         <v>42766</v>
       </c>
@@ -3354,17 +3348,17 @@
       <c r="D123" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E123" s="14">
-        <v>-1E-3</v>
-      </c>
-      <c r="F123" s="14">
-        <v>-1E-3</v>
-      </c>
-      <c r="G123" s="14">
-        <v>-1E-3</v>
-      </c>
-    </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E123" s="12">
+        <v>-1E-3</v>
+      </c>
+      <c r="F123" s="12">
+        <v>-1E-3</v>
+      </c>
+      <c r="G123" s="12">
+        <v>-1E-3</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A124" s="8">
         <v>42810</v>
       </c>
@@ -3377,17 +3371,17 @@
       <c r="D124" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E124" s="14">
-        <v>-1E-3</v>
-      </c>
-      <c r="F124" s="14">
-        <v>-1E-3</v>
-      </c>
-      <c r="G124" s="14">
-        <v>-1E-3</v>
-      </c>
-    </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E124" s="12">
+        <v>-1E-3</v>
+      </c>
+      <c r="F124" s="12">
+        <v>-1E-3</v>
+      </c>
+      <c r="G124" s="12">
+        <v>-1E-3</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A125" s="8">
         <v>42852</v>
       </c>
@@ -3400,17 +3394,17 @@
       <c r="D125" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E125" s="14">
-        <v>-1E-3</v>
-      </c>
-      <c r="F125" s="14">
-        <v>-1E-3</v>
-      </c>
-      <c r="G125" s="14">
-        <v>-1E-3</v>
-      </c>
-    </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E125" s="12">
+        <v>-1E-3</v>
+      </c>
+      <c r="F125" s="12">
+        <v>-1E-3</v>
+      </c>
+      <c r="G125" s="12">
+        <v>-1E-3</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A126" s="8">
         <v>42902</v>
       </c>
@@ -3423,17 +3417,17 @@
       <c r="D126" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E126" s="14">
-        <v>-1E-3</v>
-      </c>
-      <c r="F126" s="14">
-        <v>-1E-3</v>
-      </c>
-      <c r="G126" s="14">
-        <v>-1E-3</v>
-      </c>
-    </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E126" s="12">
+        <v>-1E-3</v>
+      </c>
+      <c r="F126" s="12">
+        <v>-1E-3</v>
+      </c>
+      <c r="G126" s="12">
+        <v>-1E-3</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A127" s="8">
         <v>42936</v>
       </c>
@@ -3446,17 +3440,17 @@
       <c r="D127" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E127" s="14">
-        <v>-1E-3</v>
-      </c>
-      <c r="F127" s="14">
-        <v>-1E-3</v>
-      </c>
-      <c r="G127" s="14">
-        <v>-1E-3</v>
-      </c>
-    </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E127" s="12">
+        <v>-1E-3</v>
+      </c>
+      <c r="F127" s="12">
+        <v>-1E-3</v>
+      </c>
+      <c r="G127" s="12">
+        <v>-1E-3</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A128" s="8">
         <v>42999</v>
       </c>
@@ -3469,17 +3463,17 @@
       <c r="D128" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E128" s="14">
-        <v>-1E-3</v>
-      </c>
-      <c r="F128" s="14">
-        <v>-1E-3</v>
-      </c>
-      <c r="G128" s="14">
-        <v>-1E-3</v>
-      </c>
-    </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E128" s="12">
+        <v>-1E-3</v>
+      </c>
+      <c r="F128" s="12">
+        <v>-1E-3</v>
+      </c>
+      <c r="G128" s="12">
+        <v>-1E-3</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A129" s="8">
         <v>43039</v>
       </c>
@@ -3492,17 +3486,17 @@
       <c r="D129" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E129" s="14">
-        <v>-1E-3</v>
-      </c>
-      <c r="F129" s="14">
-        <v>-1E-3</v>
-      </c>
-      <c r="G129" s="14">
-        <v>-1E-3</v>
-      </c>
-    </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E129" s="12">
+        <v>-1E-3</v>
+      </c>
+      <c r="F129" s="12">
+        <v>-1E-3</v>
+      </c>
+      <c r="G129" s="12">
+        <v>-1E-3</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A130" s="8">
         <v>43090</v>
       </c>
@@ -3515,17 +3509,17 @@
       <c r="D130" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E130" s="14">
-        <v>-1E-3</v>
-      </c>
-      <c r="F130" s="14">
-        <v>-1E-3</v>
-      </c>
-      <c r="G130" s="14">
-        <v>-1E-3</v>
-      </c>
-    </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E130" s="12">
+        <v>-1E-3</v>
+      </c>
+      <c r="F130" s="12">
+        <v>-1E-3</v>
+      </c>
+      <c r="G130" s="12">
+        <v>-1E-3</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A131" s="8">
         <v>43123</v>
       </c>
@@ -3538,17 +3532,17 @@
       <c r="D131" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E131" s="14">
-        <v>-1E-3</v>
-      </c>
-      <c r="F131" s="14">
-        <v>-1E-3</v>
-      </c>
-      <c r="G131" s="14">
-        <v>-1E-3</v>
-      </c>
-    </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E131" s="12">
+        <v>-1E-3</v>
+      </c>
+      <c r="F131" s="12">
+        <v>-1E-3</v>
+      </c>
+      <c r="G131" s="12">
+        <v>-1E-3</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A132" s="8">
         <v>43168</v>
       </c>
@@ -3561,17 +3555,17 @@
       <c r="D132" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E132" s="14">
-        <v>-1E-3</v>
-      </c>
-      <c r="F132" s="14">
-        <v>-1E-3</v>
-      </c>
-      <c r="G132" s="14">
-        <v>-1E-3</v>
-      </c>
-    </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E132" s="12">
+        <v>-1E-3</v>
+      </c>
+      <c r="F132" s="12">
+        <v>-1E-3</v>
+      </c>
+      <c r="G132" s="12">
+        <v>-1E-3</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A133" s="8">
         <v>43217</v>
       </c>
@@ -3584,17 +3578,17 @@
       <c r="D133" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E133" s="14">
-        <v>-1E-3</v>
-      </c>
-      <c r="F133" s="14">
-        <v>-1E-3</v>
-      </c>
-      <c r="G133" s="14">
-        <v>-1E-3</v>
-      </c>
-    </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E133" s="12">
+        <v>-1E-3</v>
+      </c>
+      <c r="F133" s="12">
+        <v>-1E-3</v>
+      </c>
+      <c r="G133" s="12">
+        <v>-1E-3</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A134" s="8">
         <v>43266</v>
       </c>
@@ -3607,17 +3601,17 @@
       <c r="D134" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E134" s="14">
-        <v>-1E-3</v>
-      </c>
-      <c r="F134" s="14">
-        <v>-1E-3</v>
-      </c>
-      <c r="G134" s="14">
-        <v>-1E-3</v>
-      </c>
-    </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E134" s="12">
+        <v>-1E-3</v>
+      </c>
+      <c r="F134" s="12">
+        <v>-1E-3</v>
+      </c>
+      <c r="G134" s="12">
+        <v>-1E-3</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A135" s="8">
         <v>43312</v>
       </c>
@@ -3630,17 +3624,17 @@
       <c r="D135" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E135" s="14">
-        <v>-1E-3</v>
-      </c>
-      <c r="F135" s="14">
-        <v>-1E-3</v>
-      </c>
-      <c r="G135" s="14">
-        <v>-1E-3</v>
-      </c>
-    </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E135" s="12">
+        <v>-1E-3</v>
+      </c>
+      <c r="F135" s="12">
+        <v>-1E-3</v>
+      </c>
+      <c r="G135" s="12">
+        <v>-1E-3</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A136" s="8">
         <v>43362</v>
       </c>
@@ -3653,17 +3647,17 @@
       <c r="D136" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E136" s="14">
-        <v>-1E-3</v>
-      </c>
-      <c r="F136" s="14">
-        <v>-1E-3</v>
-      </c>
-      <c r="G136" s="14">
-        <v>-1E-3</v>
-      </c>
-    </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E136" s="12">
+        <v>-1E-3</v>
+      </c>
+      <c r="F136" s="12">
+        <v>-1E-3</v>
+      </c>
+      <c r="G136" s="12">
+        <v>-1E-3</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A137" s="8">
         <v>43404</v>
       </c>
@@ -3676,17 +3670,17 @@
       <c r="D137" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E137" s="14">
-        <v>-1E-3</v>
-      </c>
-      <c r="F137" s="14">
-        <v>-1E-3</v>
-      </c>
-      <c r="G137" s="14">
-        <v>-1E-3</v>
-      </c>
-    </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E137" s="12">
+        <v>-1E-3</v>
+      </c>
+      <c r="F137" s="12">
+        <v>-1E-3</v>
+      </c>
+      <c r="G137" s="12">
+        <v>-1E-3</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A138" s="8">
         <v>43454</v>
       </c>
@@ -3699,17 +3693,17 @@
       <c r="D138" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E138" s="14">
-        <v>-1E-3</v>
-      </c>
-      <c r="F138" s="14">
-        <v>-1E-3</v>
-      </c>
-      <c r="G138" s="14">
-        <v>-1E-3</v>
-      </c>
-    </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E138" s="12">
+        <v>-1E-3</v>
+      </c>
+      <c r="F138" s="12">
+        <v>-1E-3</v>
+      </c>
+      <c r="G138" s="12">
+        <v>-1E-3</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A139" s="8">
         <v>43488</v>
       </c>
@@ -3722,17 +3716,17 @@
       <c r="D139" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E139" s="14">
-        <v>-1E-3</v>
-      </c>
-      <c r="F139" s="14">
-        <v>-1E-3</v>
-      </c>
-      <c r="G139" s="14">
-        <v>-1E-3</v>
-      </c>
-    </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E139" s="12">
+        <v>-1E-3</v>
+      </c>
+      <c r="F139" s="12">
+        <v>-1E-3</v>
+      </c>
+      <c r="G139" s="12">
+        <v>-1E-3</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A140" s="8">
         <v>43539</v>
       </c>
@@ -3745,17 +3739,17 @@
       <c r="D140" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E140" s="14">
-        <v>-1E-3</v>
-      </c>
-      <c r="F140" s="14">
-        <v>-1E-3</v>
-      </c>
-      <c r="G140" s="14">
-        <v>-1E-3</v>
-      </c>
-    </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E140" s="12">
+        <v>-1E-3</v>
+      </c>
+      <c r="F140" s="12">
+        <v>-1E-3</v>
+      </c>
+      <c r="G140" s="12">
+        <v>-1E-3</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A141" s="8">
         <v>43580</v>
       </c>
@@ -3768,17 +3762,17 @@
       <c r="D141" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E141" s="14">
-        <v>-1E-3</v>
-      </c>
-      <c r="F141" s="14">
-        <v>-1E-3</v>
-      </c>
-      <c r="G141" s="14">
-        <v>-1E-3</v>
-      </c>
-    </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E141" s="12">
+        <v>-1E-3</v>
+      </c>
+      <c r="F141" s="12">
+        <v>-1E-3</v>
+      </c>
+      <c r="G141" s="12">
+        <v>-1E-3</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A142" s="8">
         <v>43636</v>
       </c>
@@ -3791,17 +3785,17 @@
       <c r="D142" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E142" s="14">
-        <v>-1E-3</v>
-      </c>
-      <c r="F142" s="14">
-        <v>-1E-3</v>
-      </c>
-      <c r="G142" s="14">
-        <v>-1E-3</v>
-      </c>
-    </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E142" s="12">
+        <v>-1E-3</v>
+      </c>
+      <c r="F142" s="12">
+        <v>-1E-3</v>
+      </c>
+      <c r="G142" s="12">
+        <v>-1E-3</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A143" s="8">
         <v>43676</v>
       </c>
@@ -3814,17 +3808,17 @@
       <c r="D143" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E143" s="14">
-        <v>-1E-3</v>
-      </c>
-      <c r="F143" s="14">
-        <v>-1E-3</v>
-      </c>
-      <c r="G143" s="14">
-        <v>-1E-3</v>
-      </c>
-    </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E143" s="12">
+        <v>-1E-3</v>
+      </c>
+      <c r="F143" s="12">
+        <v>-1E-3</v>
+      </c>
+      <c r="G143" s="12">
+        <v>-1E-3</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A144" s="8">
         <v>43727</v>
       </c>
@@ -3837,17 +3831,17 @@
       <c r="D144" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E144" s="14">
-        <v>-1E-3</v>
-      </c>
-      <c r="F144" s="14">
-        <v>-1E-3</v>
-      </c>
-      <c r="G144" s="14">
-        <v>-1E-3</v>
-      </c>
-    </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E144" s="12">
+        <v>-1E-3</v>
+      </c>
+      <c r="F144" s="12">
+        <v>-1E-3</v>
+      </c>
+      <c r="G144" s="12">
+        <v>-1E-3</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A145" s="8">
         <v>43769</v>
       </c>
@@ -3860,17 +3854,17 @@
       <c r="D145" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E145" s="14">
-        <v>-1E-3</v>
-      </c>
-      <c r="F145" s="14">
-        <v>-1E-3</v>
-      </c>
-      <c r="G145" s="14">
-        <v>-1E-3</v>
-      </c>
-    </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E145" s="12">
+        <v>-1E-3</v>
+      </c>
+      <c r="F145" s="12">
+        <v>-1E-3</v>
+      </c>
+      <c r="G145" s="12">
+        <v>-1E-3</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A146" s="8">
         <v>43818</v>
       </c>
@@ -3883,17 +3877,17 @@
       <c r="D146" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E146" s="14">
-        <v>-1E-3</v>
-      </c>
-      <c r="F146" s="14">
-        <v>-1E-3</v>
-      </c>
-      <c r="G146" s="14">
-        <v>-1E-3</v>
-      </c>
-    </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E146" s="12">
+        <v>-1E-3</v>
+      </c>
+      <c r="F146" s="12">
+        <v>-1E-3</v>
+      </c>
+      <c r="G146" s="12">
+        <v>-1E-3</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A147" s="8">
         <v>43851</v>
       </c>
@@ -3906,17 +3900,17 @@
       <c r="D147" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E147" s="14">
-        <v>-1E-3</v>
-      </c>
-      <c r="F147" s="14">
-        <v>-1E-3</v>
-      </c>
-      <c r="G147" s="14">
-        <v>-1E-3</v>
-      </c>
-    </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E147" s="12">
+        <v>-1E-3</v>
+      </c>
+      <c r="F147" s="12">
+        <v>-1E-3</v>
+      </c>
+      <c r="G147" s="12">
+        <v>-1E-3</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A148" s="8">
         <v>43906</v>
       </c>
@@ -3929,17 +3923,17 @@
       <c r="D148" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E148" s="14">
-        <v>-1E-3</v>
-      </c>
-      <c r="F148" s="14">
-        <v>-1E-3</v>
-      </c>
-      <c r="G148" s="14">
-        <v>-1E-3</v>
-      </c>
-    </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E148" s="12">
+        <v>-1E-3</v>
+      </c>
+      <c r="F148" s="12">
+        <v>-1E-3</v>
+      </c>
+      <c r="G148" s="12">
+        <v>-1E-3</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A149" s="8">
         <v>43948</v>
       </c>
@@ -3952,17 +3946,17 @@
       <c r="D149" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E149" s="14">
-        <v>-1E-3</v>
-      </c>
-      <c r="F149" s="14">
-        <v>-1E-3</v>
-      </c>
-      <c r="G149" s="14">
-        <v>-1E-3</v>
-      </c>
-    </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E149" s="12">
+        <v>-1E-3</v>
+      </c>
+      <c r="F149" s="12">
+        <v>-1E-3</v>
+      </c>
+      <c r="G149" s="12">
+        <v>-1E-3</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A150" s="8">
         <v>43973</v>
       </c>
@@ -3975,14 +3969,14 @@
       <c r="D150" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E150" s="14">
-        <v>-1E-3</v>
-      </c>
-      <c r="G150" s="14">
-        <v>-1E-3</v>
-      </c>
-    </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E150" s="12">
+        <v>-1E-3</v>
+      </c>
+      <c r="G150" s="12">
+        <v>-1E-3</v>
+      </c>
+    </row>
+    <row r="151" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A151" s="8">
         <v>43998</v>
       </c>
@@ -3995,14 +3989,14 @@
       <c r="D151" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E151" s="14">
-        <v>-1E-3</v>
-      </c>
-      <c r="G151" s="14">
-        <v>-1E-3</v>
-      </c>
-    </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E151" s="12">
+        <v>-1E-3</v>
+      </c>
+      <c r="G151" s="12">
+        <v>-1E-3</v>
+      </c>
+    </row>
+    <row r="152" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A152" s="8">
         <v>44027</v>
       </c>
@@ -4015,17 +4009,17 @@
       <c r="D152" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E152" s="14">
-        <v>-1E-3</v>
-      </c>
-      <c r="F152" s="14">
-        <v>-1E-3</v>
-      </c>
-      <c r="G152" s="14">
-        <v>-1E-3</v>
-      </c>
-    </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E152" s="12">
+        <v>-1E-3</v>
+      </c>
+      <c r="F152" s="12">
+        <v>-1E-3</v>
+      </c>
+      <c r="G152" s="12">
+        <v>-1E-3</v>
+      </c>
+    </row>
+    <row r="153" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A153" s="8">
         <v>44091</v>
       </c>
@@ -4038,17 +4032,17 @@
       <c r="D153" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E153" s="14">
-        <v>-1E-3</v>
-      </c>
-      <c r="F153" s="14">
-        <v>-1E-3</v>
-      </c>
-      <c r="G153" s="14">
-        <v>-1E-3</v>
-      </c>
-    </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E153" s="12">
+        <v>-1E-3</v>
+      </c>
+      <c r="F153" s="12">
+        <v>-1E-3</v>
+      </c>
+      <c r="G153" s="12">
+        <v>-1E-3</v>
+      </c>
+    </row>
+    <row r="154" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A154" s="8">
         <v>44133</v>
       </c>
@@ -4061,17 +4055,17 @@
       <c r="D154" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E154" s="14">
-        <v>-1E-3</v>
-      </c>
-      <c r="F154" s="14">
-        <v>-1E-3</v>
-      </c>
-      <c r="G154" s="14">
-        <v>-1E-3</v>
-      </c>
-    </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E154" s="12">
+        <v>-1E-3</v>
+      </c>
+      <c r="F154" s="12">
+        <v>-1E-3</v>
+      </c>
+      <c r="G154" s="12">
+        <v>-1E-3</v>
+      </c>
+    </row>
+    <row r="155" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A155" s="8">
         <v>44183</v>
       </c>
@@ -4084,17 +4078,17 @@
       <c r="D155" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E155" s="14">
-        <v>-1E-3</v>
-      </c>
-      <c r="F155" s="14">
-        <v>-1E-3</v>
-      </c>
-      <c r="G155" s="14">
-        <v>-1E-3</v>
-      </c>
-    </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E155" s="12">
+        <v>-1E-3</v>
+      </c>
+      <c r="F155" s="12">
+        <v>-1E-3</v>
+      </c>
+      <c r="G155" s="12">
+        <v>-1E-3</v>
+      </c>
+    </row>
+    <row r="156" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A156" s="8">
         <v>44217</v>
       </c>
@@ -4107,17 +4101,17 @@
       <c r="D156" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E156" s="14">
-        <v>-1E-3</v>
-      </c>
-      <c r="F156" s="14">
-        <v>-1E-3</v>
-      </c>
-      <c r="G156" s="14">
-        <v>-1E-3</v>
-      </c>
-    </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E156" s="12">
+        <v>-1E-3</v>
+      </c>
+      <c r="F156" s="12">
+        <v>-1E-3</v>
+      </c>
+      <c r="G156" s="12">
+        <v>-1E-3</v>
+      </c>
+    </row>
+    <row r="157" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A157" s="8">
         <v>44274</v>
       </c>
@@ -4130,17 +4124,17 @@
       <c r="D157" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E157" s="14">
-        <v>-1E-3</v>
-      </c>
-      <c r="F157" s="14">
-        <v>-1E-3</v>
-      </c>
-      <c r="G157" s="14">
-        <v>-1E-3</v>
-      </c>
-    </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E157" s="12">
+        <v>-1E-3</v>
+      </c>
+      <c r="F157" s="12">
+        <v>-1E-3</v>
+      </c>
+      <c r="G157" s="12">
+        <v>-1E-3</v>
+      </c>
+    </row>
+    <row r="158" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A158" s="8">
         <v>44313</v>
       </c>
@@ -4153,17 +4147,17 @@
       <c r="D158" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E158" s="14">
-        <v>-1E-3</v>
-      </c>
-      <c r="F158" s="14">
-        <v>-1E-3</v>
-      </c>
-      <c r="G158" s="14">
-        <v>-1E-3</v>
-      </c>
-    </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E158" s="12">
+        <v>-1E-3</v>
+      </c>
+      <c r="F158" s="12">
+        <v>-1E-3</v>
+      </c>
+      <c r="G158" s="12">
+        <v>-1E-3</v>
+      </c>
+    </row>
+    <row r="159" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A159" s="8">
         <v>44365</v>
       </c>
@@ -4176,17 +4170,17 @@
       <c r="D159" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E159" s="14">
-        <v>-1E-3</v>
-      </c>
-      <c r="F159" s="14">
-        <v>-1E-3</v>
-      </c>
-      <c r="G159" s="14">
-        <v>-1E-3</v>
-      </c>
-    </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E159" s="12">
+        <v>-1E-3</v>
+      </c>
+      <c r="F159" s="12">
+        <v>-1E-3</v>
+      </c>
+      <c r="G159" s="12">
+        <v>-1E-3</v>
+      </c>
+    </row>
+    <row r="160" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A160" s="8">
         <v>44393</v>
       </c>
@@ -4199,17 +4193,17 @@
       <c r="D160" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E160" s="14">
-        <v>-1E-3</v>
-      </c>
-      <c r="F160" s="14">
-        <v>-1E-3</v>
-      </c>
-      <c r="G160" s="14">
-        <v>-1E-3</v>
-      </c>
-    </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E160" s="12">
+        <v>-1E-3</v>
+      </c>
+      <c r="F160" s="12">
+        <v>-1E-3</v>
+      </c>
+      <c r="G160" s="12">
+        <v>-1E-3</v>
+      </c>
+    </row>
+    <row r="161" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A161" s="8">
         <v>44461</v>
       </c>
@@ -4222,14 +4216,14 @@
       <c r="D161" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E161" s="14">
-        <v>-1E-3</v>
-      </c>
-      <c r="G161" s="14">
-        <v>-1E-3</v>
-      </c>
-    </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E161" s="12">
+        <v>-1E-3</v>
+      </c>
+      <c r="G161" s="12">
+        <v>-1E-3</v>
+      </c>
+    </row>
+    <row r="162" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A162" s="8">
         <v>44497</v>
       </c>
@@ -4242,17 +4236,17 @@
       <c r="D162" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E162" s="14">
-        <v>-1E-3</v>
-      </c>
-      <c r="F162" s="14">
-        <v>-1E-3</v>
-      </c>
-      <c r="G162" s="14">
-        <v>-1E-3</v>
-      </c>
-    </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E162" s="12">
+        <v>-1E-3</v>
+      </c>
+      <c r="F162" s="12">
+        <v>-1E-3</v>
+      </c>
+      <c r="G162" s="12">
+        <v>-1E-3</v>
+      </c>
+    </row>
+    <row r="163" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A163" s="8">
         <v>44547</v>
       </c>
@@ -4265,17 +4259,17 @@
       <c r="D163" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E163" s="14">
-        <v>-1E-3</v>
-      </c>
-      <c r="F163" s="14">
-        <v>-1E-3</v>
-      </c>
-      <c r="G163" s="14">
-        <v>-1E-3</v>
-      </c>
-    </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E163" s="12">
+        <v>-1E-3</v>
+      </c>
+      <c r="F163" s="12">
+        <v>-1E-3</v>
+      </c>
+      <c r="G163" s="12">
+        <v>-1E-3</v>
+      </c>
+    </row>
+    <row r="164" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A164" s="8">
         <v>44579</v>
       </c>
@@ -4288,17 +4282,17 @@
       <c r="D164" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E164" s="14">
-        <v>-1E-3</v>
-      </c>
-      <c r="F164" s="14">
-        <v>-1E-3</v>
-      </c>
-      <c r="G164" s="14">
-        <v>-1E-3</v>
-      </c>
-    </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E164" s="12">
+        <v>-1E-3</v>
+      </c>
+      <c r="F164" s="12">
+        <v>-1E-3</v>
+      </c>
+      <c r="G164" s="12">
+        <v>-1E-3</v>
+      </c>
+    </row>
+    <row r="165" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A165" s="8">
         <v>44638</v>
       </c>
@@ -4311,17 +4305,17 @@
       <c r="D165" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E165" s="14">
-        <v>-1E-3</v>
-      </c>
-      <c r="F165" s="14">
-        <v>-1E-3</v>
-      </c>
-      <c r="G165" s="14">
-        <v>-1E-3</v>
-      </c>
-    </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E165" s="12">
+        <v>-1E-3</v>
+      </c>
+      <c r="F165" s="12">
+        <v>-1E-3</v>
+      </c>
+      <c r="G165" s="12">
+        <v>-1E-3</v>
+      </c>
+    </row>
+    <row r="166" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A166" s="8">
         <v>44679</v>
       </c>
@@ -4334,17 +4328,17 @@
       <c r="D166" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E166" s="14">
-        <v>-1E-3</v>
-      </c>
-      <c r="F166" s="14">
-        <v>-1E-3</v>
-      </c>
-      <c r="G166" s="14">
-        <v>-1E-3</v>
-      </c>
-    </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E166" s="12">
+        <v>-1E-3</v>
+      </c>
+      <c r="F166" s="12">
+        <v>-1E-3</v>
+      </c>
+      <c r="G166" s="12">
+        <v>-1E-3</v>
+      </c>
+    </row>
+    <row r="167" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A167" s="8">
         <v>44729</v>
       </c>
@@ -4357,17 +4351,17 @@
       <c r="D167" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E167" s="14">
-        <v>-1E-3</v>
-      </c>
-      <c r="F167" s="14">
-        <v>-1E-3</v>
-      </c>
-      <c r="G167" s="14">
-        <v>-1E-3</v>
-      </c>
-    </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E167" s="12">
+        <v>-1E-3</v>
+      </c>
+      <c r="F167" s="12">
+        <v>-1E-3</v>
+      </c>
+      <c r="G167" s="12">
+        <v>-1E-3</v>
+      </c>
+    </row>
+    <row r="168" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A168" s="8">
         <v>44729</v>
       </c>
@@ -4380,14 +4374,14 @@
       <c r="D168" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E168" s="14">
-        <v>-1E-3</v>
-      </c>
-      <c r="G168" s="14">
-        <v>-1E-3</v>
-      </c>
-    </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E168" s="12">
+        <v>-1E-3</v>
+      </c>
+      <c r="G168" s="12">
+        <v>-1E-3</v>
+      </c>
+    </row>
+    <row r="169" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A169" s="8">
         <v>44763</v>
       </c>
@@ -4400,17 +4394,17 @@
       <c r="D169" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E169" s="14">
-        <v>-1E-3</v>
-      </c>
-      <c r="F169" s="14">
-        <v>-1E-3</v>
-      </c>
-      <c r="G169" s="14">
-        <v>-1E-3</v>
-      </c>
-    </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E169" s="12">
+        <v>-1E-3</v>
+      </c>
+      <c r="F169" s="12">
+        <v>-1E-3</v>
+      </c>
+      <c r="G169" s="12">
+        <v>-1E-3</v>
+      </c>
+    </row>
+    <row r="170" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A170" s="8">
         <v>44826</v>
       </c>
@@ -4423,17 +4417,17 @@
       <c r="D170" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E170" s="14">
-        <v>-1E-3</v>
-      </c>
-      <c r="F170" s="14">
-        <v>-1E-3</v>
-      </c>
-      <c r="G170" s="14">
-        <v>-1E-3</v>
-      </c>
-    </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E170" s="12">
+        <v>-1E-3</v>
+      </c>
+      <c r="F170" s="12">
+        <v>-1E-3</v>
+      </c>
+      <c r="G170" s="12">
+        <v>-1E-3</v>
+      </c>
+    </row>
+    <row r="171" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A171" s="8">
         <v>44862</v>
       </c>
@@ -4446,17 +4440,17 @@
       <c r="D171" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E171" s="14">
-        <v>-1E-3</v>
-      </c>
-      <c r="F171" s="14">
-        <v>-1E-3</v>
-      </c>
-      <c r="G171" s="14">
-        <v>-1E-3</v>
-      </c>
-    </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E171" s="12">
+        <v>-1E-3</v>
+      </c>
+      <c r="F171" s="12">
+        <v>-1E-3</v>
+      </c>
+      <c r="G171" s="12">
+        <v>-1E-3</v>
+      </c>
+    </row>
+    <row r="172" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A172" s="8">
         <v>44915</v>
       </c>
@@ -4469,17 +4463,17 @@
       <c r="D172" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E172" s="14">
-        <v>-1E-3</v>
-      </c>
-      <c r="F172" s="14">
-        <v>-1E-3</v>
-      </c>
-      <c r="G172" s="14">
-        <v>-1E-3</v>
-      </c>
-    </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E172" s="12">
+        <v>-1E-3</v>
+      </c>
+      <c r="F172" s="12">
+        <v>-1E-3</v>
+      </c>
+      <c r="G172" s="12">
+        <v>-1E-3</v>
+      </c>
+    </row>
+    <row r="173" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A173" s="8">
         <v>44944</v>
       </c>
@@ -4492,17 +4486,17 @@
       <c r="D173" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E173" s="14">
-        <v>-1E-3</v>
-      </c>
-      <c r="F173" s="14">
-        <v>-1E-3</v>
-      </c>
-      <c r="G173" s="14">
-        <v>-1E-3</v>
-      </c>
-    </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E173" s="12">
+        <v>-1E-3</v>
+      </c>
+      <c r="F173" s="12">
+        <v>-1E-3</v>
+      </c>
+      <c r="G173" s="12">
+        <v>-1E-3</v>
+      </c>
+    </row>
+    <row r="174" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A174" s="8">
         <v>44995</v>
       </c>
@@ -4515,17 +4509,17 @@
       <c r="D174" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E174" s="14">
-        <v>-1E-3</v>
-      </c>
-      <c r="F174" s="14">
-        <v>-1E-3</v>
-      </c>
-      <c r="G174" s="14">
-        <v>-1E-3</v>
-      </c>
-    </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E174" s="12">
+        <v>-1E-3</v>
+      </c>
+      <c r="F174" s="12">
+        <v>-1E-3</v>
+      </c>
+      <c r="G174" s="12">
+        <v>-1E-3</v>
+      </c>
+    </row>
+    <row r="175" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A175" s="8">
         <v>45044</v>
       </c>
@@ -4538,17 +4532,17 @@
       <c r="D175" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E175" s="14">
-        <v>-1E-3</v>
-      </c>
-      <c r="F175" s="14">
-        <v>-1E-3</v>
-      </c>
-      <c r="G175" s="14">
-        <v>-1E-3</v>
-      </c>
-    </row>
-    <row r="176" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E175" s="12">
+        <v>-1E-3</v>
+      </c>
+      <c r="F175" s="12">
+        <v>-1E-3</v>
+      </c>
+      <c r="G175" s="12">
+        <v>-1E-3</v>
+      </c>
+    </row>
+    <row r="176" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A176" s="8">
         <v>45093</v>
       </c>
@@ -4561,17 +4555,17 @@
       <c r="D176" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E176" s="14">
-        <v>-1E-3</v>
-      </c>
-      <c r="F176" s="14">
-        <v>-1E-3</v>
-      </c>
-      <c r="G176" s="14">
-        <v>-1E-3</v>
-      </c>
-    </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E176" s="12">
+        <v>-1E-3</v>
+      </c>
+      <c r="F176" s="12">
+        <v>-1E-3</v>
+      </c>
+      <c r="G176" s="12">
+        <v>-1E-3</v>
+      </c>
+    </row>
+    <row r="177" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A177" s="8">
         <v>45135</v>
       </c>
@@ -4584,17 +4578,17 @@
       <c r="D177" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E177" s="14">
-        <v>-1E-3</v>
-      </c>
-      <c r="F177" s="14">
-        <v>-1E-3</v>
-      </c>
-      <c r="G177" s="14">
-        <v>-1E-3</v>
-      </c>
-    </row>
-    <row r="178" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E177" s="12">
+        <v>-1E-3</v>
+      </c>
+      <c r="F177" s="12">
+        <v>-1E-3</v>
+      </c>
+      <c r="G177" s="12">
+        <v>-1E-3</v>
+      </c>
+    </row>
+    <row r="178" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A178" s="8">
         <v>45191</v>
       </c>
@@ -4607,17 +4601,17 @@
       <c r="D178" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E178" s="14">
-        <v>-1E-3</v>
-      </c>
-      <c r="F178" s="14">
-        <v>-1E-3</v>
-      </c>
-      <c r="G178" s="14">
-        <v>-1E-3</v>
-      </c>
-    </row>
-    <row r="179" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E178" s="12">
+        <v>-1E-3</v>
+      </c>
+      <c r="F178" s="12">
+        <v>-1E-3</v>
+      </c>
+      <c r="G178" s="12">
+        <v>-1E-3</v>
+      </c>
+    </row>
+    <row r="179" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A179" s="8">
         <v>45230</v>
       </c>
@@ -4630,17 +4624,17 @@
       <c r="D179" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E179" s="14">
-        <v>-1E-3</v>
-      </c>
-      <c r="F179" s="14">
-        <v>-1E-3</v>
-      </c>
-      <c r="G179" s="14">
-        <v>-1E-3</v>
-      </c>
-    </row>
-    <row r="180" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E179" s="12">
+        <v>-1E-3</v>
+      </c>
+      <c r="F179" s="12">
+        <v>-1E-3</v>
+      </c>
+      <c r="G179" s="12">
+        <v>-1E-3</v>
+      </c>
+    </row>
+    <row r="180" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A180" s="8">
         <v>45279</v>
       </c>
@@ -4653,17 +4647,17 @@
       <c r="D180" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E180" s="14">
-        <v>-1E-3</v>
-      </c>
-      <c r="F180" s="14">
-        <v>-1E-3</v>
-      </c>
-      <c r="G180" s="14">
-        <v>-1E-3</v>
-      </c>
-    </row>
-    <row r="181" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E180" s="12">
+        <v>-1E-3</v>
+      </c>
+      <c r="F180" s="12">
+        <v>-1E-3</v>
+      </c>
+      <c r="G180" s="12">
+        <v>-1E-3</v>
+      </c>
+    </row>
+    <row r="181" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A181" s="8">
         <v>45314</v>
       </c>
@@ -4676,17 +4670,17 @@
       <c r="D181" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E181" s="14">
-        <v>-1E-3</v>
-      </c>
-      <c r="F181" s="14">
-        <v>-1E-3</v>
-      </c>
-      <c r="G181" s="14">
-        <v>-1E-3</v>
-      </c>
-    </row>
-    <row r="182" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E181" s="12">
+        <v>-1E-3</v>
+      </c>
+      <c r="F181" s="12">
+        <v>-1E-3</v>
+      </c>
+      <c r="G181" s="12">
+        <v>-1E-3</v>
+      </c>
+    </row>
+    <row r="182" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A182" s="8">
         <v>45370</v>
       </c>
@@ -4699,17 +4693,17 @@
       <c r="D182" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E182" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="F182" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="G182" s="14">
-        <v>-1E-3</v>
-      </c>
-    </row>
-    <row r="183" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E182" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="F182" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="G182" s="12">
+        <v>-1E-3</v>
+      </c>
+    </row>
+    <row r="183" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A183" s="8">
         <v>45408</v>
       </c>
@@ -4722,17 +4716,17 @@
       <c r="D183" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E183" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="F183" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="G183" s="14">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="184" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E183" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="F183" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="G183" s="12">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="184" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A184" s="8">
         <v>45457</v>
       </c>
@@ -4745,17 +4739,17 @@
       <c r="D184" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E184" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="F184" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="G184" s="14">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="185" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E184" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="F184" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="G184" s="12">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="185" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A185" s="8">
         <v>45504</v>
       </c>
@@ -4768,17 +4762,17 @@
       <c r="D185" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E185" s="14">
+      <c r="E185" s="12">
         <v>2.5000000000000001E-3</v>
       </c>
-      <c r="F185" s="14">
-        <v>1E-3</v>
-      </c>
-      <c r="G185" s="14">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="186" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="F185" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="G185" s="12">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="186" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A186" s="8">
         <v>45555</v>
       </c>
@@ -4791,17 +4785,17 @@
       <c r="D186" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E186" s="14">
+      <c r="E186" s="12">
         <v>2.5000000000000001E-3</v>
       </c>
-      <c r="F186" s="14">
+      <c r="F186" s="12">
         <v>2.5000000000000001E-3</v>
       </c>
-      <c r="G186" s="14">
+      <c r="G186" s="12">
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="187" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="187" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A187" s="8">
         <v>45596</v>
       </c>
@@ -4814,17 +4808,17 @@
       <c r="D187" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E187" s="14">
+      <c r="E187" s="12">
         <v>2.5000000000000001E-3</v>
       </c>
-      <c r="F187" s="14">
+      <c r="F187" s="12">
         <v>2.5000000000000001E-3</v>
       </c>
-      <c r="G187" s="14">
+      <c r="G187" s="12">
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="188" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="188" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A188" s="8">
         <v>45645</v>
       </c>
@@ -4837,17 +4831,17 @@
       <c r="D188" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E188" s="14">
+      <c r="E188" s="12">
         <v>2.5000000000000001E-3</v>
       </c>
-      <c r="F188" s="14">
+      <c r="F188" s="12">
         <v>2.5000000000000001E-3</v>
       </c>
-      <c r="G188" s="14">
+      <c r="G188" s="12">
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="189" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="189" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A189" s="8">
         <v>45681</v>
       </c>
@@ -4860,17 +4854,17 @@
       <c r="D189" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E189" s="14">
+      <c r="E189" s="12">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="F189" s="14">
+      <c r="F189" s="12">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="G189" s="14">
+      <c r="G189" s="12">
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="190" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="190" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A190" s="8">
         <v>45735</v>
       </c>
@@ -4883,17 +4877,17 @@
       <c r="D190" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E190" s="14">
+      <c r="E190" s="12">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="F190" s="14">
+      <c r="F190" s="12">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="G190" s="14">
+      <c r="G190" s="12">
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="191" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="191" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A191" s="8">
         <v>45778</v>
       </c>
@@ -4906,17 +4900,17 @@
       <c r="D191" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E191" s="14">
+      <c r="E191" s="12">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="F191" s="14">
+      <c r="F191" s="12">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="G191" s="14">
+      <c r="G191" s="12">
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="192" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="192" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A192" s="8">
         <v>45825</v>
       </c>
@@ -4929,17 +4923,17 @@
       <c r="D192" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E192" s="14">
+      <c r="E192" s="12">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="F192" s="14">
+      <c r="F192" s="12">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="G192" s="14">
+      <c r="G192" s="12">
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="193" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="193" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A193" s="8">
         <v>45869</v>
       </c>
@@ -4952,17 +4946,17 @@
       <c r="D193" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E193" s="14">
+      <c r="E193" s="12">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="F193" s="14">
+      <c r="F193" s="12">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="G193" s="14">
+      <c r="G193" s="12">
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="194" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="194" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A194" s="8">
         <v>45919</v>
       </c>
@@ -4975,17 +4969,17 @@
       <c r="D194" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E194" s="14">
+      <c r="E194" s="12">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="F194" s="14">
+      <c r="F194" s="12">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="G194" s="14">
+      <c r="G194" s="12">
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="195" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="195" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A195" s="8">
         <v>45960</v>
       </c>
@@ -4998,17 +4992,17 @@
       <c r="D195" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E195" s="14">
+      <c r="E195" s="12">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="F195" s="14">
+      <c r="F195" s="12">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="G195" s="14">
+      <c r="G195" s="12">
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="196" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="196" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A196" s="8">
         <v>46010</v>
       </c>
@@ -5021,18 +5015,18 @@
       <c r="D196" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E196" s="14">
+      <c r="E196" s="12">
         <v>7.4999999999999997E-3</v>
       </c>
-      <c r="F196" s="14">
+      <c r="F196" s="12">
         <v>7.4999999999999997E-3</v>
       </c>
-      <c r="G196" s="14">
+      <c r="G196" s="12">
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="197" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A197" s="11">
+    <row r="197" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A197" s="8">
         <v>46045</v>
       </c>
       <c r="B197" s="8">
@@ -5044,21 +5038,21 @@
       <c r="D197" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E197" s="14">
+      <c r="E197" s="12">
         <v>7.4999999999999997E-3</v>
       </c>
-      <c r="F197" s="14">
+      <c r="F197" s="12">
         <v>7.4999999999999997E-3</v>
       </c>
-      <c r="G197" s="14">
+      <c r="G197" s="12">
         <v>7.4999999999999997E-3</v>
       </c>
     </row>
-    <row r="198" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A198" s="11">
+    <row r="198" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A198" s="8">
         <v>46100</v>
       </c>
-      <c r="B198" s="11">
+      <c r="B198" s="8">
         <v>46100</v>
       </c>
       <c r="C198" s="9">
@@ -5067,21 +5061,21 @@
       <c r="D198" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E198" s="14">
+      <c r="E198" s="12">
         <v>7.4999999999999997E-3</v>
       </c>
-      <c r="F198" s="14">
+      <c r="F198" s="12">
         <v>7.4999999999999997E-3</v>
       </c>
-      <c r="G198" s="14">
+      <c r="G198" s="12">
         <v>7.4999999999999997E-3</v>
       </c>
     </row>
-    <row r="199" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A199" s="11">
+    <row r="199" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A199" s="8">
         <v>46140</v>
       </c>
-      <c r="B199" s="11">
+      <c r="B199" s="8">
         <v>46140</v>
       </c>
       <c r="C199" s="9">
@@ -5090,21 +5084,21 @@
       <c r="D199" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E199" s="14">
+      <c r="E199" s="12">
         <v>7.4999999999999997E-3</v>
       </c>
-      <c r="F199" s="14">
+      <c r="F199" s="12">
         <v>7.4999999999999997E-3</v>
       </c>
-      <c r="G199" s="14">
+      <c r="G199" s="12">
         <v>7.4999999999999997E-3</v>
       </c>
     </row>
-    <row r="200" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A200" s="11">
+    <row r="200" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A200" s="8">
         <v>46189</v>
       </c>
-      <c r="B200" s="11">
+      <c r="B200" s="8">
         <v>46189</v>
       </c>
       <c r="C200" s="9">
@@ -5113,21 +5107,21 @@
       <c r="D200" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E200" s="14">
+      <c r="E200" s="12">
         <v>0.01</v>
       </c>
-      <c r="F200" s="14">
+      <c r="F200" s="12">
         <v>0.01</v>
       </c>
-      <c r="G200" s="14">
+      <c r="G200" s="12">
         <v>7.4999999999999997E-3</v>
       </c>
     </row>
-    <row r="201" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A201" s="11">
+    <row r="201" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A201" s="8">
         <v>46234</v>
       </c>
-      <c r="B201" s="11">
+      <c r="B201" s="8">
         <v>46234</v>
       </c>
       <c r="C201" s="9">
@@ -5136,10 +5130,13 @@
       <c r="D201" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="F201" s="14">
+      <c r="E201" s="12">
         <v>0.01</v>
       </c>
-      <c r="G201" s="14">
+      <c r="F201" s="12">
+        <v>0.01</v>
+      </c>
+      <c r="G201" s="12">
         <v>0.01</v>
       </c>
     </row>
@@ -5153,12 +5150,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB9E5B25-827A-49DC-A0E2-CBBE95A45320}">
   <dimension ref="B2:C3"/>
-  <sheetFormatPr defaultColWidth="8.8984375" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="10.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B2" s="1" t="s">
         <v>5</v>
       </c>
@@ -5166,7 +5163,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
